--- a/igaming/clusters.xlsx
+++ b/igaming/clusters.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Method" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clusters'!$A$1:$K$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clusters'!$A$1:$N$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Members'!$A$1:$H$347</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -488,8 +488,11 @@
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="64" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="54" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,6 +548,21 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>SERP theme</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Winning format</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>SERP intent</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Members</t>
         </is>
       </c>
@@ -586,6 +604,21 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
+          <t>Fragmented SERP: Indeed job listings (DR92), Sportradar's marketing-services product page, agency strategy blog posts (DataArt, low-DR Team Catalyst DR5), an academic NIH paper and an agency listicle, with a Medium UGC post in the top 10. No single format owns the query.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
           <t>sportsbook marketing services, sports betting marketing strategies, online sportsbook marketing, sportsbook digital marketing, sportsbook marketing solutions</t>
         </is>
       </c>
@@ -632,6 +665,21 @@
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Affiliate program directories and listicles dominate (BusinessofApps, AffPaying, AskGamblers, StatsDrone) alongside program operators' own homepages (Alpha Affiliates, LivePartners) and an ad-network blog listicle (RichAds). Reddit at #3 and YouTube in the top 10 show Google rewarding UGC here.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>program directory / listicle</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>join affiliate program</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>casino affiliate program, casino affiliate programs, gambling affiliate program, affiliate casino program, affiliate casino programs, casino affiliate, online casino affiliates, best gambling affiliate programs, casino affiliates, gambling affiliate marketing software, online casino affiliate program, affiliate program casino, best casino affiliate program, casino affiliate system, top casino affiliate program, online casino affiliate programs, best igaming affiliate programs, best gambling affiliate program, best casino affiliate marketing software, affiliate program online casino, best online casino affiliate program, online gambling affiliate program, social casino affiliate program</t>
         </is>
@@ -674,6 +722,21 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
+          <t>Affiliate-SaaS vendors win with blog guides and comparison posts (Tracknow, iRev, Voluum, Affise) plus product homepages (Affilka); a DR6 exact-match domain (igamingaffiliates.io) ranks #2, signalling a beatable SERP.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>vendor blog guide</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
           <t>igaming affiliate software, igaming affiliate marketing software, igaming affiliate platform, igaming affiliate marketing, igaming affiliate marketing system, igaming affiliate system, igaming affiliate management software, igaming affiliate management service, igaming affiliate program, igaming affiliate, igaming affiliate programs, affiliate igaming, igaming affiliate news, igaming affiliate network, affiliate marketing igaming, affiliate marketing software for igaming, igaming affiliate program software, igaming affiliate marketing programs, affiliate tracking software for igaming, igaming affiliate management, igaming affiliate marketing agency, igaming affiliate management platform, what is igaming affiliate marketing, igaming affiliate marketing consulting, igaming affiliate management agency, igaming affiliate tracking platforms</t>
         </is>
       </c>
@@ -721,6 +784,21 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
+          <t>How-to guides and program listicles from ad-network/tracker blogs (RichAds, Voluum) and affiliate directories (BusinessofApps, StatsDrone, BettingUSA) fill the page; Reddit holds #1 and YouTube also ranks, a clear UGC weakness.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>how-to guide / listicle</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
           <t>gambling affiliate programs, gambling affiliate marketing, affiliate marketing gambling, online casino affiliate marketing, casino affiliate marketing, betting affiliate program, sports betting affiliate programs, betting affiliate, gambling affiliate marketing platform, casino affiliate marketing platform, sports betting affiliate marketing, sports betting affiliate program, gambling affiliate, affiliate gambling, sportsbook affiliate program, sportsbook affiliate programs, affiliate marketing casino, sports betting affiliates, affiliate gambling program, affiliate marketing sports betting, online casino affiliate, online gambling affiliate, affiliate program gambling, sport betting affiliate program, affiliate gambling marketing, betting affiliate marketing software, affiliate marketing for gambling, casino affiliate advertising, betting affiliate marketing system, sports betting affiliate traffic, sports gambling affiliate marketing, online betting affiliate program, betting affiliate marketing</t>
         </is>
       </c>
@@ -768,6 +846,21 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
+          <t>High-DR news outlets (Guardian, ESPN), industry-association trend reports (American Gaming Association), and academic/ethics pieces (NIH, Brooklyn Law) own the SERP; nothing commercial ranks and Reddit sits mid-page.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>news / research articles</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>industry reference</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
           <t>sports betting ads, sports gambling ads, sports gambling advertising, betting advertising, sportsbook advertising, online betting ads, advertising sports betting, sports betting ads examples</t>
         </is>
       </c>
@@ -815,6 +908,21 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
+          <t>Split between iGaming agency landing pages (Luvkaizen DR28, igaming.agency DR0.7, ICS Digital) and 'top agencies' listicles (Absolute Digital, HilltopAds, DR10 Redclawey); many low-DR domains plus a LinkedIn company page in the top 10 make this a soft SERP.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>agency landing page / listicle</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
           <t>igaming digital marketing, igaming content marketing, igaming digital marketing agency, igaming digital agency, igaming agency, igaming marketing services, igaming marketing company, igaming growth marketing agency, igaming content marketing agency, igaming marketing agencies, igaming digital marketing services, igaming event marketing agency</t>
         </is>
       </c>
@@ -861,6 +969,21 @@
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Consumer-facing SERP: Reddit complaints at #1, GambleAware and UK Gambling Commission pages on limiting/opting out of gambling ads, Wikipedia, and news coverage. Searchers here are mostly annoyed consumers, not advertisers.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>casino ads, online casino ads, betting ads, ads for gambling, casino game ads</t>
         </is>
@@ -903,6 +1026,21 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
+          <t>iGaming SEO agency landing pages dominate, mostly low-DR (tbd.media DR27, Qwerty Labs DR15, Naturallinks DR38) alongside GeekyTech (DR75); Trustpilot and a LinkedIn company page also rank, confirming a weak, winnable SERP.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>agency landing page</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
           <t>igaming seo</t>
         </is>
       </c>
@@ -950,6 +1088,21 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
+          <t>Policy and reference pages rule: Google Ads and Meta ad-policy documentation, UK Parliament research briefing, Wikipedia, AGA ad-spend PDF and news; Reddit appears mid-page. All-high-DR institutional SERP with no commercial players.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>policy documentation</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>policy / compliance reference</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
           <t>online casino advertising, gambling advertising regulations, online gambling ads, advertising for gambling, advertise gambling, gambling digital ads, online gambling advertising, gambling advertising regulations united states, compliant gambling advertising, gambling advertising rules</t>
         </is>
       </c>
@@ -997,6 +1150,21 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
+          <t>Land-based-leaning mix of Indeed jobs (#1), how-to guides from martech blogs (iPost, MoEngage, Cvent) and casino agency pages (Good Giant, LT Agency, DR7 Casino Marketing Bootcamp); a LinkedIn page also ranks.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>how-to guide</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
           <t>casino advertising strategies, casino digital marketing, online casino marketing strategy, casino marketing plan, online casino marketing, casino advertising channels, casino content marketing</t>
         </is>
       </c>
@@ -1043,6 +1211,21 @@
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Agency directories are the power players (Semrush Agencies DR92, Clutch DR91, Influencer Marketing Hub) interleaved with individual agency landing pages (Bird, LT Agency, Straight North, low-DR Velocity/Good Giant) and a LinkedIn UGC result.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>agency directory / listicle</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>casino marketing agency, casino digital marketing agency, betting company marketing agency, online betting marketing agency, online casino marketing agency, casino advertising agency, online casino digital marketing, gambling digital marketing agency, gambling and casino marketing agencies, casino marketing services, casino marketing consulting, gambling digital marketing, crypto casino marketing agency</t>
         </is>
@@ -1085,6 +1268,21 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
+          <t>Highly fragmented: an agency landing page, tactic articles on niche industry sites (WA Technology, DR21 Grou Global), a HilltopAds listicle, job pages (ZipRecruiter, DR1.7 igamingcareers) and LinkedIn Pulse UGC. Several sub-DR30 domains rank — weak SERP with unsettled intent.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
           <t>marketing igaming, igaming marketing strategies</t>
         </is>
       </c>
@@ -1126,6 +1324,21 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
+          <t>Step-by-step how-to guides from iGaming platform providers (SoftGamings, Sirplay, Genome, iGamingBusiness/TrueLabel, RichAds) and a law-services explainer; Reddit holds #1, exposing a UGC gap.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>how-to guide</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
           <t>how to start an online casino, how to start an online gambling business</t>
         </is>
       </c>
@@ -1173,6 +1386,21 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
+          <t>Google's own policy doc at #2, followed by blockchain-ads.com's post at #3, industry news coverage (MediaPost, SBC Americas, Bettors Insider) and a RichAds blog post; YouTube and Reddit round out the top 10. News-plus-policy SERP where BCA already ranks.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>news + policy doc</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>policy / compliance reference</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
           <t>google ads gambling, google ads gambling policy, google ads gambling policy update, can you advertise gambling on google, google ads gambling and games policy, google ads gambling certification, social casino google ads, online gambling certificate google ads, google ads casino policy, casino google ads, google ads gambling certification apply, google ads gambling license, google ads online gambling allowed countries, social casino certificate google ads</t>
         </is>
       </c>
@@ -1220,6 +1448,21 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
+          <t>Ad networks win with dedicated traffic landing pages and blog guides (RichAds /igaming-traffic, TrafficNomads DR27, Voluum, AffPapa guide, low-DR Z2A Digital); Reddit and YouTube both sit in the top 10 — a buyable SERP with UGC softness.</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>ad-network landing page / blog</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>buy traffic / choose platform</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
           <t>igaming traffic provider, buy gambling traffic, buy igaming traffic, igaming traffic for affiliates, top traffic sources igaming, quality traffic igaming offers, igaming traffic sources</t>
         </is>
       </c>
@@ -1266,6 +1509,21 @@
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Creative-inspiration SERP: example galleries (Pinterest, Behance, Ads of the World, iSpot.tv) and campaign listicles (Everything-PR, RichAds creatives post) dominate, with heavy UGC (Pinterest, YouTube playlist) in the top 10.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>creative example gallery / listicle</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>casino ad, best casino ads, casino advertising examples, creative gambling ads, best gambling ads, gambling creatives, gambling advertising examples, casino ads examples, gambling ads examples, creative casino ads</t>
         </is>
@@ -1306,6 +1564,21 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
+          <t>CRM SaaS vendor product pages (Optimove, Solitics, Groovetech) and vendor listicles (DR25 OptiKPI) rank alongside Reddit and Medium UGC and very low-DR sites (DR4.4 Quettaspins) — a weak vendor-selection SERP.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>product landing page / listicle</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
           <t>igaming crm marketing tools, crm marketing for igaming, igaming marketing crm</t>
         </is>
       </c>
@@ -1345,6 +1618,21 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
+          <t>Platform policy pages top the SERP (Facebook Business Help #1, Meta ad standards, Google Ads policy), followed by promotion-tips listicles from vendors (Selzy, PartnerMatrix, RichAds ad-network listicle, BusinessofApps, Altenar). Compliance-first, then how-to.</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>policy pages + how-to listicle</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
           <t>promote casino, how to promote a casino website, how to promote online casino, how to advertise gambling, how to run ads for betting app</t>
         </is>
       </c>
@@ -1386,6 +1674,21 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
+          <t>Affiliate-software vendors own the SERP with product pages (EveryMatrix PartnerMatrix #1, Affilka, Income Access) and vendor blog explainers (Track360 glossary, iRev, Smartico, Affise); solid mid-to-high DR throughout.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>product landing page</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
           <t>affiliate marketing software for casino, casino affiliate program software, affiliate marketing software for gambling, casino affiliate marketing tools</t>
         </is>
       </c>
@@ -1431,7 +1734,22 @@
           <t>Optimize existing page (strike zone)</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>UGC-riddled and fragmented: Pinterest boards at #1 and #4, a YouTube playlist, Wikipedia, plus a RichAds guide, an agency page (LT Agency) and a First Amendment law article. No commercial format has consolidated this SERP.</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1475,6 +1793,21 @@
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Idea/tips listicles on martech and vendor blogs win outright (Geotargetly, iPost, Odds On Promotions DR29, Selzy, Tegna, DR22 J Carcamo, MoEngage) — a classic listicle SERP with mostly mid-DR domains.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>blog listicle</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>casino marketing strategy, casino marketing strategies, online casino marketing strategies</t>
         </is>
@@ -1517,6 +1850,21 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
+          <t>Definitional content wins: Wikipedia, glossary pages (Endava, Track-style), 'what is iGaming' guides (RichAds, Aeropay, Sportsbetting Dime, DR29 Global Advisory Experts), with Reddit and LinkedIn UGC also ranking.</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>definition guide / glossary</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
           <t>igaming definition</t>
         </is>
       </c>
@@ -1563,6 +1911,21 @@
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Ad networks and ad-tech blogs dominate: ReachEffect's iGaming LP at #1, Voluum and RichAds posts, BusinessofApps creative best practices, and blockchain-ads.com's iGaming ad examples post at #10; low-DR vizibl.ai (DR8) also ranks.</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>ad-network landing page / blog</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>buy traffic / choose platform</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>igaming advertising, igaming online advertising</t>
         </is>
@@ -1605,6 +1968,21 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
+          <t>Explainer guides from iGaming platform vendors (RichAds beginners guide, SoftSwiss, BetConstruct) mixed with the BusinessofApps directory and affiliate-program pages (PartnerMatrix, Affnook, Alpha Affiliates); Reddit sits mid-page.</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>how-to guide</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
           <t>gambling affiliate marketing system</t>
         </is>
       </c>
@@ -1646,6 +2024,21 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
+          <t>Research-institution SERP: academic papers (NIH, ScienceDirect, ResearchGate-tier), UK Gambling Commission advertising rules, and industry PDFs (Responsible Gambling Council, AGA ad-spend). All high-DR; only Selzy, Elit-web and RichAds represent commercial content.</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>research / regulatory reports</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>industry reference</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
           <t>online betting marketing strategy, online gambling marketing, online gambling marketing strategy</t>
         </is>
       </c>
@@ -1687,6 +2080,21 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
+          <t>Academic and industry-research results lead (NIH #1, ResearchGate, AGA trend report) with strategy blog posts (DataArt, Elit-web) and Sportradar's product page mixed in — a reference-heavy SERP where commercial pages struggle above mid-page.</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>research + strategy blog</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>industry reference</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
           <t>betting marketing, betting digital marketing, digital marketing for betting sites</t>
         </is>
       </c>
@@ -1728,6 +2136,21 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
+          <t>Program operators' signup pages win (LivePartners, Paddy Power Partnerships, Neto Partners) alongside directories (BusinessofApps) and guides (Track360, RichAds, SoftSwiss); a LinkedIn company page at #1 shows SERP weakness.</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>program signup pages</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>join affiliate program</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
           <t>best igaming affiliate programs 2026</t>
         </is>
       </c>
@@ -1774,6 +2197,21 @@
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>'Best iGaming ad networks' listicles on ad-network blogs win (Kadam, RichAds, DR12 AllinAffiliates, blockchain-ads.com's top-gambling-ad-networks at #10) plus network landing pages (ReachEffect #1, TrafficNomads); several sub-DR15 domains rank, including DR0 taroviser.</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>blog listicle</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>buy traffic / choose platform</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>best igaming ads networks, gambling ad network, igaming ad network, gambling advertising network</t>
         </is>
@@ -1816,6 +2254,21 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
+          <t>Comparison listicles on affiliate-SaaS vendor blogs dominate (iRev, Voluum, Trackdesk, Tracknow, Track360, DR30 aff.tech) with product pages (Everflow, EveryMatrix PartnerMatrix) filling out; Reddit ranks #4.</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>comparison listicle</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
           <t>igaming affiliate management system</t>
         </is>
       </c>
@@ -1853,7 +2306,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Pure news SERP owned by top-tier outlets (BBC #1, Reuters, Washington Post, The Conversation) plus AGA and an NIH paper — uniformly very high DR, essentially unassailable without a news angle.</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>news articles</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>industry reference</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1898,6 +2366,21 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
+          <t>Ad networks win with vertical landing pages and how-to blogs (TrafficNomads DR27 at #1, Clickadu gambling-traffic LP, RichAds, Voluum, betting.partners); Reddit and a Semrush trending page also rank. Low-DR #1 signals an open SERP.</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>ad-network landing page / blog</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>buy traffic / choose platform</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
           <t>gambling traffic sources, buy casino traffic, betting traffic sources, sports betting traffic sources</t>
         </is>
       </c>
@@ -1944,6 +2427,21 @@
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Agency landing pages rank despite tiny authority (bvcompany.org DR5 holds #1 and #10, Square in the Air DR31, Samba Digital) beside the Semrush agency directory, Sportradar's services page and LinkedIn Pulse UGC — a notably weak SERP.</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>agency landing page</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>betting marketing agency, marketing agency for sports betting, sportsbook digital marketing agency, sportsbook marketing agency</t>
         </is>
@@ -1984,6 +2482,21 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
+          <t>Affiliate directories win (iGB Affiliate directory, AffCatalog, AffPapa, DR21 AffSecret, aff.studio) plus a RichAds listicle; Reddit sits at #5. Directory format plus mid-DR field.</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>program directory</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>join affiliate program</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
           <t>igaming affiliate networks list</t>
         </is>
       </c>
@@ -2023,6 +2536,21 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
+          <t>Vendor product/solution pages rank (OptiKPI, Wizards, Kanggiten, Optimove) alongside a Track360 guide, but the SERP is strikingly weak: DR1 icatalyft at #2, DR4.7 cognaix, and a LinkedIn job posting all crack the top 10.</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>product landing page</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
           <t>igaming marketing automation</t>
         </is>
       </c>
@@ -2064,6 +2592,21 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
+          <t>Casino-SEO agency landing pages win, including exact-match low-DR domains (seocasinomarketing.com DR3.1, seo.casino, DR3 Marqade) plus GeekyTech and directories (Semrush, DesignRush); a LinkedIn company page ranks #2 — soft SERP.</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>agency landing page</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
           <t>casino seo marketing services</t>
         </is>
       </c>
@@ -2110,6 +2653,21 @@
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>Meta's own properties dominate — three facebook.com help/business pages plus transparency.meta ad standards — with a Hunch how-to, GambleAware and Rest of World coverage; Reddit and BlackHatWorld UGC also rank.</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>policy documentation</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>policy / compliance reference</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>advertise gambling pop sources online, casino facebook ads, facebook gambling ads policy, facebook casino ads, casino ads on facebook</t>
         </is>
@@ -2152,6 +2710,21 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
+          <t>Email SaaS vendors win with industry solution pages and strategy guides (iPost holds three slots, UniOne, Selzy, Litmus, Evenbet); low-DR guides (DR7 Casino Marketing Bootcamp, DR16 Marketing Results) and a YouTube video also rank.</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>vendor solution page / guide</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
           <t>email marketing for gambling, casino email marketing, betting email marketing services</t>
         </is>
       </c>
@@ -2193,6 +2766,21 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
+          <t>Platform providers' product pages lead (Aristocrat Interactive #1, Gamingtec, BetConstruct, DR0.5 OHS Gaming) with provider listicles (Kodedice, AllinAffiliates, Smartico) and a SoftSwiss definition page; Reddit and LinkedIn UGC appear low in the top 10.</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>product landing page</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
           <t>white label casino affiliate program, white label igaming affiliate platform</t>
         </is>
       </c>
@@ -2232,7 +2820,22 @@
           <t>NEW page - moderately weak SERP</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>Land-based casino-management software SERP: a SoftwareReviews category page at #1, vendor product pages (Agilysys, Infor, CT Gaming, DR9 MRI AIM, DR21 Playersoft) and a Smartico listicle; YouTube ranks #9. Skews CMS/ops, not advertising.</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>product landing page</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2269,7 +2872,22 @@
           <t>NEW page - moderately weak SERP</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Totally fragmented, non-advertising SERP: foot-traffic sensor vendor (#1 Sensource), local news traffic plans, weather cams, three YouTube results, Trustpilot, and 'betting on live traffic' novelty coverage. No advertiser intent visible.</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2304,7 +2922,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>B2B SaaS and consultancy blog thought-leadership sweeps the SERP (Optimove, Dynamic Yield, Intellias, Symphony Solutions, Nuxgame, Track360, DR26 Rapidpace); one LinkedIn Pulse UGC result. Pure vendor-education play.</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>vendor blog article</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2343,6 +2976,21 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
+          <t>Affiliate networks' own pages (Gambling-Affiliation, n1.partners), directories (iGB Affiliate, DR13 AffCaptain) and listicles from ad-tech blogs (RichAds, Voluum) share the SERP with a Paysafe resource page; Reddit ranks #3.</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>directory / listicle</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>join affiliate program</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
           <t>igaming affiliate networks, igaming affiliate cpa rates</t>
         </is>
       </c>
@@ -2382,6 +3030,21 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
+          <t>Split-intent oddity: 'traffic betting' novelty content (Reddit #2, Trustpilot review of cctv-game.live, Instagram, Bitcointalk, Sigma news) collides with ad-network pages (RichAds /betting-traffic LP, TrafficGuard). Heavy UGC and no settled meaning.</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
           <t>sports betting traffic</t>
         </is>
       </c>
@@ -2421,7 +3084,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>Trend-report articles from iGaming platform vendors win (Kodedice, Rapyd, SoftSwiss report, Symphony Solutions, RichAds) plus the AGA revenue tracker and a LinkedIn Pulse piece — annual-roundup reference content.</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>trend report / blog</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>industry reference</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2460,6 +3138,21 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
+          <t>Affiliate-SaaS vendor blog and glossary pages dominate (Track360 holds three slots, DR16 Intelitics, Affilka, Post Affiliate Pro) with the StatsDrone directory and a 1xBet affiliates post — vendor-education SERP with modest competition.</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>vendor blog / glossary</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
           <t>affiliate marketing software for betting</t>
         </is>
       </c>
@@ -2499,6 +3192,21 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
+          <t>Ad networks win with vertical landing pages (Pushground, AADS) and how-to blogs (Voluum, RichAds, Adcash); X's gambling ads policy, Reddit, Instagram, and a spammy stck.me post also rank — commercial SERP with soft spots.</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>ad-network landing page / blog</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>buy traffic / choose platform</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
           <t>casino ads traffic</t>
         </is>
       </c>
@@ -2538,6 +3246,21 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
+          <t>Mixed authority SERP: legal/research pieces lead (IMGL magazine #1, Greo, NIH) followed by agency pages (DR37 Famesters, Luvkaizen), an influencer list (Viral Nation), the Semrush directory, and LinkedIn/Reddit UGC.</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
           <t>casino influencer marketing</t>
         </is>
       </c>
@@ -2577,7 +3300,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>Regulators and industry bodies own it: NY Gaming Commission #1, Mass.gov regulation text, AGA marketing code, Meta ad standards, plus ESPN news and a law-school analysis. Nearly all DR70-92 — a true compliance-reference SERP.</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>policy documentation</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>policy / compliance reference</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2612,7 +3350,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>Ad-network 'where to buy iGaming traffic' blog guides dominate (PropellerAds, AdRoll, seo.casino, Z2A) plus traffic landing pages (ReachEffect, HilltopAds); Quora is the lone UGC entry. Directly monetizable buy-traffic SERP.</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>ad-network blog guide</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>buy traffic / choose platform</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2647,7 +3400,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>Meta's own policy/help pages hold multiple slots (facebook.com #1, two transparency.meta pages) with trade news filling the rest (SBC Americas, iGaming Expert, Reuters) and a LinkedIn post; policy-doc-plus-news SERP.</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>policy documentation + news</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>policy / compliance reference</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2684,6 +3452,21 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
+          <t>Fragmented: a Behance creative gallery at #1, blockchain-ads.com's own crypto-gambling LP at #4, AADS's casino-advertising LP, near-zero-DR marketing blogs (Adspires DR0, Scale with Ascend DR0, Coinpresso DR26), Rolling Stone news and Reddit. Weak, unconsolidated SERP BCA already touches.</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
           <t>crypto casino marketing</t>
         </is>
       </c>
@@ -2721,7 +3504,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>Industry-body guidelines and policy docs win: IAB creative-guidelines PDF, Ad Standards Canada, AGA marketing code, Meta ad standards, plus BusinessofApps' creative best-practices post and an NIH paper; one DR22 agency post ranks.</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>guidelines documentation</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>policy / compliance reference</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2756,7 +3554,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>SaaS vendors dominate: tracker/CRM product pages (voluum.com, optimove.com, bloomreach.com) mixed with affiliate-software vendor blogs (track360.io, affise.com, irev.com, aff.tech) and an f6s.com software directory. All commercial DR 30-83, no UGC.</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>product landing page</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2797,7 +3610,22 @@
           <t>Optimize existing page (strike zone)</t>
         </is>
       </c>
-      <c r="K55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>Mix of affiliate-program listicles (track360.io, businessofapps.com, affpapa.com), program signup/landing pages of operators (n1.partners, starzpartners.com, cloudbet.com/affiliates) and the affpaying.com directory; a Reddit thread ranks #2, signalling a beatable SERP with mid-DR players (DR 37-86).</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>listicle + program signup pages</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>join affiliate program</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2834,6 +3662,21 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
+          <t>Push/pop ad-network blogs own this SERP: richads.com case studies and guides, pushground.com and roiads.co landing/blog pages, adcash.com; heavy UGC presence (Reddit r/PPC, afflift forum, YouTube) shows low competition. Format is how-to/case-study blog posts from networks selling the traffic.</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>ad-network blog guide</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>buy traffic / choose platform</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
           <t>casino push ads, betting push ads</t>
         </is>
       </c>
@@ -2875,6 +3718,21 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
+          <t>Ad-network 'best gambling ad networks' listicles dominate (richads.com, blockchain-ads.com already at #3, hilltopads.com, trafficnomads.com, betconstruct.com) alongside network landing pages (aads.com, pushground.com, reacheffect.com); Reddit and LinkedIn UGC in top 10 confirm a soft SERP.</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>blog listicle</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>buy traffic / choose platform</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
           <t>betting ad network</t>
         </is>
       </c>
@@ -2914,7 +3772,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>Fragmented SERP of crypto-marketing agency landing pages (coinpresso.io, seo.casino), ad-network product pages (aads.com, cointraffic.com), affiliate blog guides (affpapa.com, scaleo.io) and a gpwa.org forum thread at #3; many low-DR sites (DR 16-38) and forum/YouTube UGC signal weak competition.</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>buy traffic / choose platform</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2951,6 +3824,21 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
+          <t>Affiliate-software and tracker blogs (track360.io, irev.com, voluum.com, affnook.com, maxweb.com, partnermatrix.com) publish benchmark/data posts; very low-DR pages rank high (redclawey.com DR 10 at #2, smsedge.com DR 8) plus YouTube/Reddit UGC — a soft data-driven SERP.</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>data/benchmark blog post</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
           <t>igaming affiliate revenue share commission rates</t>
         </is>
       </c>
@@ -2990,6 +3878,21 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
+          <t>PPC agency service pages (elit-web.com, optimum7.com, ppcjuice.com, circusppc.com, wiredmedia.co.uk) and agency-directory listings (clutch.co DR 91) compete with tracker blogs (voluum.com, clickguard.com, propellerads.com); LinkedIn UGC and DR 3-15 domains in top 10 show weakness.</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>agency service page</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
           <t>igaming ppc</t>
         </is>
       </c>
@@ -3027,7 +3930,22 @@
           <t>NEW page - moderately weak SERP</t>
         </is>
       </c>
-      <c r="K61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Google's own policy documentation ranks #1 (support.google.com DR 99) but the rest is thin: a Reddit AMA at #2, low-DR agency pages (ppcjuice.com DR 3), tracker blog (voluum.com) and LinkedIn posts — very shallow SERP beyond the policy page.</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>policy doc + how-to guides</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3062,7 +3980,22 @@
           <t>NEW page - moderately weak SERP</t>
         </is>
       </c>
-      <c r="K62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>TikTok's own help-center policy articles occupy most positions (ads.tiktok.com help pages), padded by BlackHatWorld and Reddit threads and one DR 32 blog guide — platform documentation is the answer, with only UGC as third-party competition.</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>policy documentation</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>policy / compliance reference</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3097,7 +4030,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>All high-DR authority: regulators and industry bodies (gamblingcommission.gov.uk, americangaming.org, bettingandgamingcouncil.com, massgaming.com), academic papers (pmc.ncbi.nlm.nih.gov) and research PDFs. Zero commercial players and zero UGC — a hard, informational/regulatory SERP.</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>policy documentation</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>policy / compliance reference</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3134,7 +4082,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K64" s="4" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>Affiliate directories and listicles (businessofapps.com, zorbasmedia.com, 1xbetaffiliates.net) mixed with explainer posts on CPA-vs-revshare from affiliate-software vendors (track360.io, irev.com) and operator program blogs (n1.partners, roiads.co); one Reddit thread in top 10.</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>listicle + explainer post</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>join affiliate program</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3169,7 +4132,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>A Reddit thread ranks #1, followed by affiliate-program directories (affpaying.com, postaffiliatepro.com, 15m.com), listicles (affpapa.com, affnook.com) and direct program signup pages (alpha-affiliates.com, nowpayments.io) — directory/listing formats win on a soft SERP.</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>program directory/listicle</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>join affiliate program</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3204,7 +4182,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>Fragmented mix of small casino-marketing agencies (vallomedia.com DR 27, playerperformancegroup.com DR 19) and general casino-marketing strategy guides (moengage.com, alphametic.com, elit-web.com), plus a LinkedIn post and casinovendors.com directory listing — no dominant format, mostly land-based casino angle.</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3239,7 +4232,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K67" s="4" t="inlineStr"/>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>B2B iGaming supplier pages and blogs (sportradar.com, netrefer.com, theaffiliateplatform.com, igaming.createit.com) mixed with off-topic results (law firm M&amp;A page, Wikipedia, Quora, investor news) — an unfocused SERP where strategy-guide content from platform vendors wins.</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>vendor blog guide</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3278,6 +4286,21 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
+          <t>Very weak SERP: DR 0-26 sites (affiliace.digital, rapidpace.com, marqade.com) plus LinkedIn/Quora/YouTube UGC rank alongside ad-network blog guides (richads.com, reacheffect.com, voluum.com); conversion/how-to blog posts win with almost no authority competition.</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>how-to guide</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
           <t>online casino traffic</t>
         </is>
       </c>
@@ -3315,7 +4338,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K69" s="4" t="inlineStr"/>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>Affiliate-network and tracker blogs (tracknow.io, roiads.co, richads.com, betting.partners, pmaffiliates.com) publish traffic-source guides; affiliatefix forum thread and Reddit in top 10 plus a DR 6 site show low competition.</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>blog guide (traffic sources)</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3352,7 +4390,22 @@
           <t>NEW page - moderately weak SERP</t>
         </is>
       </c>
-      <c r="K70" s="4" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>Fragmented: job listings (indeed.com), Reddit thread, casinovendors.com supplier directory, agency pages (bird.marketing, designrush.com directory) and iGaming media-buying guides (affise.com, betboyz.com DR 13); no clear winning format — intent splits between hiring, agencies and how-to.</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3387,7 +4440,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K71" s="4" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>Split between high-DR policy/regulatory pages (support.google.com, transparency.meta.com, gamblingcommission.gov.uk, an NCBI paper) and practitioner guides from agencies/media (tegna.com, elit-web.com, licensegentlemen.com); a Reddit AMA sits in the top 10. Compliance-aware best-practice guides win.</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>how-to guide + policy docs</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3424,7 +4492,22 @@
           <t>NEW page - moderately weak SERP</t>
         </is>
       </c>
-      <c r="K72" s="4" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>Affiliate-tooling vendors and directories rank: businessofapps.com casino list at #1, tracking-software pages (trafficmanager.com, affilka.com), tool listicles (smartico.ai, allinaffiliates.com DR 12) and ad-network blogs (richads.com); Quora and Reddit UGC in top 10 signal softness.</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>tool listicle</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3459,7 +4542,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>Competitor ad-network listicles (richads.com, monetag.com, propellerads.com) and software-review directories (capterra.com DR 91) compete with Adsterra's own 'alternatives' blog posts ranking for its brand; one Reddit thread. Classic alternatives-listicle SERP.</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>alternatives listicle</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>compare options (listicle)</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3496,7 +4594,22 @@
           <t>NEW page - moderately weak SERP</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr"/>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>Very weak SERP: influencer-agency landing pages and blogs (famesters.com DR 37, luvkaizen.com, awisee.com) mixed with DR 0.7-16 blogs, Reddit and LinkedIn UGC — no authority owns this; agency service pages and guides both rank.</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>agency page / blog guide</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3533,7 +4646,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K75" s="4" t="inlineStr"/>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>Long-form 'complete guide' blog posts from affiliate-software and ad-network vendors (tracknow.io, irev.com, richads.com, bloomreach.com gated guide) plus low-DR agency blogs (rainmakeragency.ai, smsedge.com DR 8, envisioner.io DR 14) — beatable guide-format SERP.</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>long-form guide</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3568,7 +4696,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K76" s="4" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>Dominated by academic and public-interest research (bristol.ac.uk report, Springer, NCBI, theguardian.com, bi.team, greo.ca) on gambling-ad harms plus Meta's help page — a high-DR harm-focused informational SERP, not a practitioner one; hard for commercial content.</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>research report/news</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>industry reference</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3605,7 +4748,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>A DR 2.6 agency page ranks #1 (tentenseven.com) ahead of industry-body data (americangaming.org), vendor strategy blogs (tecpinion.com, gammastack.com, optimove.com, richads.com) and a LinkedIn post at #2 — extremely soft SERP won by strategy guides and agency pages.</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>strategy blog guide</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3644,6 +4802,21 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
+          <t>Casino-marketing strategy guides from agencies and martech vendors (alphametic.com, elit-web.com, selzy.com, moengage.com, cvent.com, scaleo.io funnel post); #1 is a DR 24 blog (translationroyale.com) and YouTube ranks mid-page — funnel/strategy blog posts win a soft SERP.</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>strategy blog guide</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
           <t>casino online marketing</t>
         </is>
       </c>
@@ -3681,7 +4854,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr"/>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>Explainer posts from affiliate-software vendors (track360.io, irev.com, voluum.com, affcatalog.com glossary) plus businessofapps.com revshare listicle and richads.com program listicle; LinkedIn and Reddit UGC in top 10.</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>explainer blog post</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3718,7 +4906,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr"/>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>Small specialist agency pages (andava.com, socialtrend.co.uk, luvkaizen.com) and vendor blog tips (incomeaccess.com, bgaming.com, voluum.com) with a LinkedIn article at #3 — low-competition SERP split between agency service pages and tips posts.</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>agency page / tips post</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3753,7 +4956,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K81" s="4" t="inlineStr"/>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>Fragmented: agency directories (agencies.semrush.com, topdevelopers.co), academic papers (NCBI, sciencedirect.com), strategy blogs (aads.com, alphametic.com) and SaaS solution pages (optimove.com) — mixed intent with no dominant format.</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3788,7 +5006,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K82" s="4" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>Program directories and listicles win: businessofapps.com, mylead.global, zorbasmedia.com, 15m.com, plus track360.io educational hub pages and goaffiliates.com signup page at #1 (DR 39); a Reddit thread at #2 shows softness.</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>program directory/listicle</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>join affiliate program</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3825,7 +5058,22 @@
           <t>NEW page - moderately weak SERP</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>Retention/acquisition strategy blog posts from iGaming platform vendors and agencies (selzy.com, everymatrix.com, lt.agency, moengage.com, track360.io glossary); YouTube and Quora UGC in the top 10 and low-DR entrants (envisioner.io DR 14) make it beatable.</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>strategy blog guide</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3860,7 +5108,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K84" s="4" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>Research and news dominate (bristol.ac.uk, NCBI, norc.org, espn.com) but practitioner content ranks too (contentstadium.com content-ideas post, smartico.ai strategies, elit-web.com) — hybrid SERP leaning informational with high-DR studies.</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>research + strategy posts</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3895,7 +5158,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K85" s="4" t="inlineStr"/>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>B2B esports-odds and platform vendors (oddin.gg, gr8.tech, rebelbetting.com), market-research reports (businessresearchinsights.com) and industry media (sigma.world, digiday.com) — all mid-to-high DR blog/strategy content, no UGC; guide posts from suppliers win.</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>vendor blog guide</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3930,7 +5208,22 @@
           <t>NEW page - moderately weak SERP</t>
         </is>
       </c>
-      <c r="K86" s="4" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>Weak, fragmented SERP: two Reddit threads and a LinkedIn company page in the top 5, job boards (indeed.com, djinni.co), one affise.com guide and a DR 13 blog at #2 — how-to content from vendors barely competes with UGC and jobs listings.</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>mixed/fragmented</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3965,7 +5258,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K87" s="4" t="inlineStr"/>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>Trend-report roundups from iGaming suppliers and ad networks (bgaming.com, richads.com, softwaremind.com, evenbetgaming.com), industry-body data (americangaming.org), appsflyer.com report and a SOFTSWISS report on Scribd — annual trends listicle format wins.</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>trends report/listicle</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>industry reference</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4000,7 +5308,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K88" s="4" t="inlineStr"/>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>Pop/push ad networks own the SERP with explainer and buy pages (richads.com what-is post, reacheffect.com buy-popunder page, roiads.co, activerevenue.com, kadam.net, lospollos.com) plus businessofapps.com; a BlackHatWorld thread and DR 11 site in top 10 confirm low difficulty.</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>ad-network explainer/landing</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>buy traffic / choose platform</t>
+        </is>
+      </c>
+      <c r="N88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4035,7 +5358,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K89" s="4" t="inlineStr"/>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>High-DR data sources dominate: americangaming.org report and PDF at #2-3, trade press (sbcamericas.com, emarketer.com, espn.com) and statistics hubs (rg.org); LinkedIn and Facebook posts fill the tail. A stats/data-report SERP.</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>data report/statistics page</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>industry reference</t>
+        </is>
+      </c>
+      <c r="N89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4070,7 +5408,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K90" s="4" t="inlineStr"/>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>Software-review directories dominate (g2.com, capterra.com, getapp.ca DR 57-91) alongside HilltopAds' own pages ranking for its brand, a comparison page (adspyglass.com) and monetag.com listicle; Reddit and YouTube in top 10.</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>review-directory alternatives page</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>compare options (listicle)</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4105,7 +5458,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K91" s="4" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>PropellerAds' own domain holds four spots (its 'alternatives to X' blog posts plus homepage), with richads.com competitor listicle at #2, review directories (g2.com, cuspera.com) and a Reddit thread — alternatives listicles and review pages win.</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>alternatives listicle</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>compare options (listicle)</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4140,7 +5508,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K92" s="4" t="inlineStr"/>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>Regulator and industry-body documentation leads (gamblingcommission.gov.uk, americangaming.org, adstandards.ca, Xiaomi platform policy) but commercial compliance guides also rank (richads.com, adspyder.io, oddsindex.com DR 36); one Quora thread — compliance-guide content can compete.</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>policy docs + compliance guide</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>policy / compliance reference</t>
+        </is>
+      </c>
+      <c r="N92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4175,7 +5558,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K93" s="4" t="inlineStr"/>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>Microsoft's own properties monopolize the SERP (about.ads.microsoft.com policy pages, forms and change logs, learn.microsoft.com — DR 96) with only searchenginejournal.com and a small consultancy commenting; effectively unwinnable brand-policy SERP.</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>policy documentation</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>policy / compliance reference</t>
+        </is>
+      </c>
+      <c r="N93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4210,7 +5608,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K94" s="4" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>Platform policy pages dominate: Taboola's own casino/gambling policy FAQ and playbook PDF, plus Meta, AdRoll and NY gaming-commission policy pages; Reddit and YouTube fill gaps — official documentation is what ranks.</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>policy documentation</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>policy / compliance reference</t>
+        </is>
+      </c>
+      <c r="N94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4247,7 +5660,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K95" s="4" t="inlineStr"/>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>Fraud-prevention and KYC vendors own it with explainer blogs (group-ib.com, sumsub.com, gbg.com, paysafe.com, bluepear.net) plus affiliate-software posts (irev.com); all solid DR 38-81 except one Instagram post — educational vendor content wins.</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>vendor explainer post</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4284,7 +5712,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K96" s="4" t="inlineStr"/>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>Split SERP: affiliate-marketing explainers from trackers (voluum.com #1, irev.com, richads.com) and agency pages (sambadigital.com, lengreo.com list) against job boards (ziprecruiter.com, igamingcareers.co) — guide content wins the marketing intent.</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>blog guide</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4319,7 +5762,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K97" s="4" t="inlineStr"/>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>Benchmark/rate explainer posts from affiliate-software and network blogs (bigbetty.io CPA-tiers post, track360.io, partnermatrix.com, propellerads.com, voluum.com, affnook.com glossary); DR 8-13 sites rank (smsedge.com #2, affcaptain.com) — soft data-oriented SERP.</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>data/benchmark blog post</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4354,7 +5812,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K98" s="4" t="inlineStr"/>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>Attribution SaaS vendors rank with product/solution pages (intelitics.com DR 16, singular.net, adjust.com, violetgrowth.com) and software listicles/guides (affise.com, hockeystack.com, track360.io learn hub); low-DR specialists at the top signal a winnable vendor SERP.</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>product landing page</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>choose vendor/tool</t>
+        </is>
+      </c>
+      <c r="N98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4389,7 +5862,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K99" s="4" t="inlineStr"/>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>Program directories and comparison pages (businessofapps.com, statsdrone.com, affpaying.com) plus payout-model explainers (irev.com, track360.io glossary) and a program landing page (alpha-affiliates.com); no UGC, mid-high DR.</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>program directory/explainer</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>join affiliate program</t>
+        </is>
+      </c>
+      <c r="N99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4424,7 +5912,22 @@
           <t>NEW page - moderately weak SERP</t>
         </is>
       </c>
-      <c r="K100" s="4" t="inlineStr"/>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>Weak SERP of crypto/iGaming agency blogs (surgence.io, coinpresso.io, kolhq.com DR 4) with blockchain-ads.com already at #6, a LinkedIn pulse at #4 and a podcast page at #3 — low-DR strategy guides win easily.</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>strategy blog guide</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4459,7 +5962,22 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K101" s="4" t="inlineStr"/>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>Beginner-guide blog posts from affiliate software and ad networks (irev.com, richads.com, softswiss.com, statsdrone.com) plus niche sites (mercurytheme.com, highstakesdb.com, paylinedata.com); YouTube at #5 — long-form guides win.</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>long-form guide</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4494,7 +6012,22 @@
           <t>NEW page - moderately weak SERP</t>
         </is>
       </c>
-      <c r="K102" s="4" t="inlineStr"/>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>SMS-platform vendor pages and blogs dominate (clickatell.com, springbig.com, smsedge.com academy, texcellsms.com, optikpi.com) with a DR 11 page at #1 (mamonty.com) and LinkedIn in the tail — very soft vendor-content SERP.</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>vendor blog/service page</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4529,10 +6062,25 @@
           <t>NEW page - competitive SERP, needs authority</t>
         </is>
       </c>
-      <c r="K103" s="4" t="inlineStr"/>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>Email-platform and list vendors rank (litmus.com industry page at #2, hotsol.net, mailcheck.co, dmdatabases.com list page, bvcompany.org DR 5 service page) plus a UNLV thesis and YouTube — fragmented, low-DR, easily winnable.</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>vendor guide/service page</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>learn / how-to</t>
+        </is>
+      </c>
+      <c r="N103" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K103"/>
+  <autoFilter ref="A1:N103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
